--- a/update.xlsx
+++ b/update.xlsx
@@ -12,63 +12,105 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="8ArbSZxORg/fEt/WTfNCuPwKzTuKVPQ54HByX2zXHX0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId8" roundtripDataChecksum="DvifC5bxWtwtX6lW0yFsWnNmGGyxuM28UWoEFQQIC24="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="253">
   <si>
     <t>image</t>
   </si>
   <si>
+    <t>url</t>
+  </si>
+  <si>
     <t>title</t>
   </si>
   <si>
-    <t>url</t>
+    <t>category</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
-    <t>category</t>
-  </si>
-  <si>
     <t>link</t>
   </si>
   <si>
     <t>technologies</t>
   </si>
   <si>
+    <t>full-ms2.jpg</t>
+  </si>
+  <si>
+    <t>platform</t>
+  </si>
+  <si>
+    <t>nom</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=wvIpljmNIc4</t>
+  </si>
+  <si>
+    <t>Plan-de-travail-1-copie-4.jpg</t>
+  </si>
+  <si>
     <t>highlight</t>
   </si>
   <si>
-    <t>Plan-de-travail-1-copie-4.jpg</t>
-  </si>
-  <si>
-    <t>platform</t>
-  </si>
-  <si>
-    <t>full-ms2.jpg</t>
-  </si>
-  <si>
     <t>Tennis Winner</t>
   </si>
   <si>
-    <t>nom</t>
-  </si>
-  <si>
     <t>Qui a gagné les derniers tournois majeurs et JO ?</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=wvIpljmNIc4</t>
-  </si>
-  <si>
     <t>https://tennisgsolympicsscores-cmxidknbazy5swry5voadm.streamlit.app/</t>
   </si>
   <si>
+    <t>Entreprise</t>
+  </si>
+  <si>
+    <t>interview</t>
+  </si>
+  <si>
+    <t>évènementiel</t>
+  </si>
+  <si>
+    <t>Interview d'une alumni de IonisSTM</t>
+  </si>
+  <si>
+    <t>full-h.jpg</t>
+  </si>
+  <si>
+    <t>youtube</t>
+  </si>
+  <si>
+    <t>Mélissa Sari, Architecte Solutions Cloud Low-Code - Microsoft</t>
+  </si>
+  <si>
+    <t>Plan-de-travail-1-copie-6.jpg</t>
+  </si>
+  <si>
+    <t>https://youtube.com/watch?v=9_obNHjZqxU</t>
+  </si>
+  <si>
+    <t>inv.jpg</t>
+  </si>
+  <si>
+    <t>portrait</t>
+  </si>
+  <si>
+    <t>Interview pour l'Etudiant</t>
+  </si>
+  <si>
+    <t>Plan-de-travail-1-copie-10.jpg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/shorts/usTOedYqH6o</t>
+  </si>
+  <si>
     <t>data</t>
   </si>
   <si>
@@ -78,190 +120,223 @@
     <t>tennisstats.png</t>
   </si>
   <si>
-    <t>interview</t>
-  </si>
-  <si>
-    <t>Interview d'une alumni de IonisSTM</t>
-  </si>
-  <si>
-    <t>youtube</t>
-  </si>
-  <si>
-    <t>Mélissa Sari, Architecte Solutions Cloud Low-Code - Microsoft</t>
-  </si>
-  <si>
-    <t>https://youtube.com/watch?v=9_obNHjZqxU</t>
+    <t>autre</t>
+  </si>
+  <si>
+    <t>Micro-trottoir pour Europe1</t>
+  </si>
+  <si>
+    <t>portfolio.jpeg</t>
+  </si>
+  <si>
+    <t>pub</t>
+  </si>
+  <si>
+    <t>https://youtu.be/5-04jVYDd1E</t>
+  </si>
+  <si>
+    <t>Plan-de-travail-1-copie.jpg</t>
   </si>
   <si>
     <t>oui</t>
   </si>
   <si>
+    <t>Journée PTCE avec Mediatico</t>
+  </si>
+  <si>
     <t>Geocom Networks</t>
   </si>
   <si>
+    <t>https://youtube.com/watch?v=bu3uCbQYuMM</t>
+  </si>
+  <si>
     <t>Un site complet réalisé sur Webflow</t>
   </si>
   <si>
     <t>https://www.geocom-networks.com/</t>
   </si>
   <si>
-    <t>Interview pour l'Etudiant</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/shorts/usTOedYqH6o</t>
-  </si>
-  <si>
-    <t>autre</t>
-  </si>
-  <si>
-    <t>Micro-trottoir pour Europe1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/5-04jVYDd1E</t>
-  </si>
-  <si>
-    <t>évènementiel</t>
-  </si>
-  <si>
-    <t>Journée PTCE avec Mediatico</t>
-  </si>
-  <si>
-    <t>https://youtube.com/watch?v=bu3uCbQYuMM</t>
+    <t>Plan-de-travail-1-copie-5.jpg</t>
+  </si>
+  <si>
+    <t>full-6pages2.jpg</t>
   </si>
   <si>
     <t>Séminaire musicale, l'Agence Musicale</t>
   </si>
   <si>
+    <t>https://youtube.com/shorts/Z0cDNZFFeJc</t>
+  </si>
+  <si>
+    <t>web</t>
+  </si>
+  <si>
+    <t>Webflow</t>
+  </si>
+  <si>
+    <t>geocom.png</t>
+  </si>
+  <si>
+    <t>info.jpg</t>
+  </si>
+  <si>
+    <t>Plan-de-travail-1-copie-11.jpg</t>
+  </si>
+  <si>
+    <t>Ce portfolio</t>
+  </si>
+  <si>
+    <t>Frontend en Nest JS, backend/api en Nest JS avec appel vers une Google Sheet en base de données,</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>NextJS, NestJS</t>
+  </si>
+  <si>
+    <t>portfolio.png</t>
+  </si>
+  <si>
+    <t>motion design</t>
+  </si>
+  <si>
+    <t>Montage pour Les Numériques</t>
+  </si>
+  <si>
+    <t>full-mars.jpg</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=fDTtN0rGHU0</t>
   </si>
   <si>
-    <t>Plan-de-travail-1-copie-6.jpg</t>
-  </si>
-  <si>
-    <t>Entreprise</t>
-  </si>
-  <si>
-    <t>full-h.jpg</t>
+    <t>Plan-de-travail-1-copie-8.jpg</t>
+  </si>
+  <si>
+    <t>GitHub</t>
+  </si>
+  <si>
+    <t>maquettes2.jpg</t>
+  </si>
+  <si>
+    <t>Consultez mon GitHub pour d'autres projets !</t>
   </si>
   <si>
     <t>Interview d'un alumni de IonisSTM</t>
   </si>
   <si>
+    <t>https://github.com/tangmomb</t>
+  </si>
+  <si>
     <t>https://youtu.be/40BPQr2v3ak</t>
   </si>
   <si>
-    <t>portrait</t>
-  </si>
-  <si>
-    <t>Plan-de-travail-1-copie-10.jpg</t>
+    <t>Plan-de-travail-1-copie-7.jpg</t>
   </si>
   <si>
     <t>Interview lors d'un évènement RH</t>
   </si>
   <si>
+    <t>all</t>
+  </si>
+  <si>
     <t>https://youtube.com/watch?v=LxIOw1f2qEY</t>
   </si>
   <si>
-    <t>inv.jpg</t>
-  </si>
-  <si>
-    <t>pub</t>
-  </si>
-  <si>
-    <t>Plan-de-travail-1-copie.jpg</t>
+    <t>github.png</t>
+  </si>
+  <si>
+    <t>sedd3.jpg</t>
+  </si>
+  <si>
+    <t>Plan-de-travail-1-copie-9.jpg</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=FrPdaw0-5MU</t>
   </si>
   <si>
-    <t>portfolio.jpeg</t>
-  </si>
-  <si>
-    <t>Plan-de-travail-1-copie-5.jpg</t>
-  </si>
-  <si>
-    <t>motion design</t>
+    <t>Cavanine</t>
+  </si>
+  <si>
+    <t>Site e-commerce</t>
+  </si>
+  <si>
+    <t>WordPress</t>
+  </si>
+  <si>
+    <t>cavanine.png</t>
+  </si>
+  <si>
+    <t>portfolio (1).jpeg</t>
+  </si>
+  <si>
+    <t>bookUTP-v1v2.jpg</t>
   </si>
   <si>
     <t>Statistiques du Big 3, tennis</t>
   </si>
   <si>
+    <t>Plan-de-travail-1-copie-2.jpg</t>
+  </si>
+  <si>
+    <t>https://youtube.com/shorts/5czr8QAv6J4</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>KissnFly Films</t>
+  </si>
+  <si>
+    <t>bleu.jpg</t>
+  </si>
+  <si>
+    <t>Site portfolio</t>
+  </si>
+  <si>
+    <t>https://www.kissnflyfilms.com/</t>
+  </si>
+  <si>
     <t>https://youtu.be/1RVzuZIR_GA</t>
   </si>
   <si>
-    <t>Plan-de-travail-1-copie-11.jpg</t>
+    <t>Plan-de-travail-1.jpg</t>
   </si>
   <si>
     <t>Motion BPCE - Paris 2024</t>
   </si>
   <si>
-    <t>web</t>
-  </si>
-  <si>
-    <t>Webflow</t>
-  </si>
-  <si>
-    <t>geocom.png</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=SU_FRERE-OI</t>
   </si>
   <si>
-    <t>full-6pages2.jpg</t>
-  </si>
-  <si>
-    <t>Ce portfolio</t>
-  </si>
-  <si>
-    <t>Frontend en Nest JS, backend/api en Nest JS avec appel vers une Google Sheet en base de données,</t>
-  </si>
-  <si>
-    <t>#</t>
+    <t>sedd2.png</t>
+  </si>
+  <si>
+    <t>kissnfly.png</t>
+  </si>
+  <si>
+    <t>Plan-de-travail-1-copie-3.jpg</t>
   </si>
   <si>
     <t>Interview d'une étudiante de IonisSTM</t>
   </si>
   <si>
-    <t>NextJS, NestJS</t>
-  </si>
-  <si>
-    <t>portfolio.png</t>
-  </si>
-  <si>
-    <t>Plan-de-travail-1-copie-8.jpg</t>
-  </si>
-  <si>
     <t>https://youtube.com/watch?v=91ei--pNwqk</t>
   </si>
   <si>
-    <t>info.jpg</t>
-  </si>
-  <si>
-    <t>GitHub</t>
-  </si>
-  <si>
-    <t>Consultez mon GitHub pour d'autres projets !</t>
+    <t>maquettes11.jpg</t>
   </si>
   <si>
     <t>Journée recrutement stagiaire chez Vertone</t>
   </si>
   <si>
-    <t>https://github.com/tangmomb</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=X7dsQwjsI8I</t>
   </si>
   <si>
-    <t>Plan-de-travail-1-copie-7.jpg</t>
-  </si>
-  <si>
-    <t>full-mars.jpg</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>github.png</t>
+    <t>full-photo2.JPG</t>
+  </si>
+  <si>
+    <t>SalesEvent2019.jpg</t>
   </si>
   <si>
     <t>Interview d'une invitée pour IonisSTM</t>
@@ -270,46 +345,28 @@
     <t>https://www.youtube.com/watch?v=57NmEpSwCUI</t>
   </si>
   <si>
-    <t>Plan-de-travail-1-copie-9.jpg</t>
-  </si>
-  <si>
-    <t>Cavanine</t>
-  </si>
-  <si>
-    <t>Site e-commerce</t>
-  </si>
-  <si>
-    <t>WordPress</t>
-  </si>
-  <si>
-    <t>maquettes2.jpg</t>
-  </si>
-  <si>
-    <t>cavanine.png</t>
+    <t>full-photo6.JPG</t>
   </si>
   <si>
     <t>Interview intervenant de IonisSTM</t>
   </si>
   <si>
+    <t>full-tennisstat.jpg</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=gIhCBY6jvPM</t>
   </si>
   <si>
-    <t>non</t>
-  </si>
-  <si>
-    <t>KissnFly Films</t>
-  </si>
-  <si>
-    <t>Site portfolio</t>
-  </si>
-  <si>
-    <t>https://www.kissnflyfilms.com/</t>
-  </si>
-  <si>
-    <t>sedd3.jpg</t>
-  </si>
-  <si>
-    <t>Plan-de-travail-1-copie-2.jpg</t>
+    <t>full-photo12.JPG</t>
+  </si>
+  <si>
+    <t>Création</t>
+  </si>
+  <si>
+    <t>portfolio (2).jpeg</t>
+  </si>
+  <si>
+    <t>full-NadalMoon.jpg</t>
   </si>
   <si>
     <t>Soirée alumni pour Epitech EMBA</t>
@@ -318,16 +375,7 @@
     <t>https://vimeo.com/1164394075</t>
   </si>
   <si>
-    <t>kissnfly.png</t>
-  </si>
-  <si>
-    <t>portfolio (1).jpeg</t>
-  </si>
-  <si>
-    <t>bookUTP-v1v2.jpg</t>
-  </si>
-  <si>
-    <t>Plan-de-travail-1.jpg</t>
+    <t>full-photo13.JPG</t>
   </si>
   <si>
     <t xml:space="preserve">Interview d'une avocate </t>
@@ -339,10 +387,10 @@
     <t>https://vimeo.com/1164395172</t>
   </si>
   <si>
-    <t>Plan-de-travail-1-copie-3.jpg</t>
-  </si>
-  <si>
-    <t>bleu.jpg</t>
+    <t>1.jpg</t>
+  </si>
+  <si>
+    <t>full-photo14.JPG</t>
   </si>
   <si>
     <t>Interview d'un avocat</t>
@@ -351,64 +399,55 @@
     <t>https://youtu.be/pws2feJlrPU</t>
   </si>
   <si>
-    <t>sedd2.png</t>
-  </si>
-  <si>
-    <t>full-photo2.JPG</t>
+    <t>_DSC3490-copie.jpeg</t>
+  </si>
+  <si>
+    <t>_DSC1998-copie-3.jpeg</t>
   </si>
   <si>
     <t>https://youtu.be/y8Rwyb0kb1c</t>
   </si>
   <si>
+    <t>_DSC3479-copie.jpeg</t>
+  </si>
+  <si>
+    <t>2-light.jpg</t>
+  </si>
+  <si>
     <t>https://youtu.be/ValL8-Enf6Y</t>
   </si>
   <si>
-    <t>maquettes11.jpg</t>
-  </si>
-  <si>
-    <t>full-photo6.JPG</t>
+    <t>_DSC3903-copie.jpeg</t>
   </si>
   <si>
     <t>Clip musical pour Paola</t>
   </si>
   <si>
+    <t>full-etpourqq.PNG</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=atI5WH1soVk</t>
   </si>
   <si>
-    <t>SalesEvent2019.jpg</t>
-  </si>
-  <si>
-    <t>full-photo12.JPG</t>
+    <t>_DSC4241-copie.jpeg</t>
   </si>
   <si>
     <t>https://youtu.be/hB4oCJv8pzc</t>
   </si>
   <si>
-    <t>full-tennisstat.jpg</t>
-  </si>
-  <si>
-    <t>full-photo13.JPG</t>
+    <t>1-rouge-light.jpg</t>
   </si>
   <si>
     <t>Atelier création jeu vidéo dans un lycée</t>
   </si>
   <si>
-    <t>Création</t>
-  </si>
-  <si>
-    <t>portfolio (2).jpeg</t>
-  </si>
-  <si>
-    <t>full-NadalMoon.jpg</t>
-  </si>
-  <si>
-    <t>1.jpg</t>
+    <t>_DSC3204-copie-2.jpeg</t>
   </si>
   <si>
     <t>https://youtu.be/xnJv9fk8HP0</t>
   </si>
   <si>
-    <t>_DSC1998-copie-3.jpeg</t>
+    <t>full-yt.jpg</t>
   </si>
   <si>
     <t>Ouverture d'un nouveau magasin</t>
@@ -417,7 +456,10 @@
     <t>https://youtu.be/d762ILlbUmg</t>
   </si>
   <si>
-    <t>2-light.jpg</t>
+    <t>_DSC5444.jpeg</t>
+  </si>
+  <si>
+    <t>2-light-2.jpg</t>
   </si>
   <si>
     <t>Publicité produit orthopédique</t>
@@ -426,16 +468,16 @@
     <t>https://www.youtube.com/shorts/aWaLj4P2xs0</t>
   </si>
   <si>
-    <t>full-etpourqq.PNG</t>
+    <t>_DSC5911.jpeg</t>
   </si>
   <si>
     <t>https://www.youtube.com/shorts/Za_OGvK5KOM</t>
   </si>
   <si>
-    <t>full-photo14.JPG</t>
-  </si>
-  <si>
-    <t>1-rouge-light.jpg</t>
+    <t>2-light-1.jpg</t>
+  </si>
+  <si>
+    <t>_DSC5804.jpeg</t>
   </si>
   <si>
     <t>Micro-trottoir avec Enora Malagré</t>
@@ -444,7 +486,7 @@
     <t>https://www.youtube.com/watch?v=rmiCN1r7Mek</t>
   </si>
   <si>
-    <t>full-yt.jpg</t>
+    <t>_DSC0716.jpeg</t>
   </si>
   <si>
     <t>Interview d'un étudiant de IonisSTM</t>
@@ -453,22 +495,16 @@
     <t>https://www.youtube.com/watch?v=7bxFaga0pNg</t>
   </si>
   <si>
-    <t>_DSC3490-copie.jpeg</t>
-  </si>
-  <si>
-    <t>2-light-2.jpg</t>
+    <t>_DSC1104.jpeg</t>
   </si>
   <si>
     <t>https://www.youtube.com/shorts/HGq0PWS_M9g</t>
   </si>
   <si>
-    <t>2-light-1.jpg</t>
-  </si>
-  <si>
     <t>https://youtube.com/watch?v=XU_o7vZf7QI</t>
   </si>
   <si>
-    <t>_DSC3479-copie.jpeg</t>
+    <t>_DSC5326.jpeg</t>
   </si>
   <si>
     <t>Rafa Nadal on The Moon</t>
@@ -477,6 +513,9 @@
     <t>https://youtube.com/watch?v=cvzaU5twAMI</t>
   </si>
   <si>
+    <t>_DSC1211.jpeg</t>
+  </si>
+  <si>
     <t>Présentation application TakeOrNot</t>
   </si>
   <si>
@@ -489,7 +528,7 @@
     <t>https://youtube.com/watch?v=XKpYWwLj6MA?si=G79l_T2nzzpAkwIf</t>
   </si>
   <si>
-    <t>_DSC3903-copie.jpeg</t>
+    <t>_DSC2431-copie.jpeg</t>
   </si>
   <si>
     <t>Soirée entreprise Everysens</t>
@@ -498,30 +537,33 @@
     <t>https://youtube.com/watch?v=Xwqmhu_YWXc?si=xPkTAzvzaPC1Jhsa</t>
   </si>
   <si>
+    <t>_DSC2427-copie.jpeg</t>
+  </si>
+  <si>
     <t>Interview dirigeant pour Teamstarter</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=f8p4nxbkWtk</t>
   </si>
   <si>
-    <t>_DSC4241-copie.jpeg</t>
-  </si>
-  <si>
     <t>Publicité pour l'application Vinidaily</t>
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=OistFy3ap7w</t>
   </si>
   <si>
+    <t>_DSC7241-1.jpeg</t>
+  </si>
+  <si>
     <t>https://vimeo.com/916451147?share=copy</t>
   </si>
   <si>
-    <t>_DSC3204-copie-2.jpeg</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=dj6TuHGayDY</t>
   </si>
   <si>
+    <t>_DSC2801-copie.jpeg</t>
+  </si>
+  <si>
     <t>https://vimeo.com/1002401043</t>
   </si>
   <si>
@@ -531,16 +573,22 @@
     <t>https://vimeo.com/916451519</t>
   </si>
   <si>
+    <t>_DSC3231-copie.jpeg</t>
+  </si>
+  <si>
     <t>https://youtube.com/watch?v=RxVIb12xS_c</t>
   </si>
   <si>
     <t>Présentation d'une solution Worldline</t>
   </si>
   <si>
+    <t>_DSC2635-copie.jpeg</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=8ZaTgjBxoOo</t>
   </si>
   <si>
-    <t>_DSC5444.jpeg</t>
+    <t>DSC2922.jpeg</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=tc9ilRbJwfA</t>
@@ -549,16 +597,16 @@
     <t>Évènement Smartbox/Karmine</t>
   </si>
   <si>
-    <t>_DSC5911.jpeg</t>
-  </si>
-  <si>
     <t>https://youtube.com/watch?v=rY6cCenSuoc</t>
   </si>
   <si>
+    <t>_DSC6848-copie.jpeg</t>
+  </si>
+  <si>
     <t>https://youtube.com/watch?v=ky5iPI0M9Yw</t>
   </si>
   <si>
-    <t>_DSC5804.jpeg</t>
+    <t>DSC5588.jpeg</t>
   </si>
   <si>
     <t>Best of du salon SIMA 2022</t>
@@ -567,7 +615,7 @@
     <t>https://www.youtube.com/watch?v=-bIUB_idBuU</t>
   </si>
   <si>
-    <t>_DSC0716.jpeg</t>
+    <t>_DSC6800-copie.jpeg</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=YArESRAO628</t>
@@ -576,33 +624,24 @@
     <t>Campagne de pub parisienne H&amp;M</t>
   </si>
   <si>
-    <t>_DSC1104.jpeg</t>
-  </si>
-  <si>
     <t>https://youtube.com/watch?v=-L5ZtPZc2BQ</t>
   </si>
   <si>
+    <t>_DSC3612-copie.jpeg</t>
+  </si>
+  <si>
     <t>Bimedia et Teamstarter, anniversaire</t>
   </si>
   <si>
-    <t>_DSC5326.jpeg</t>
-  </si>
-  <si>
     <t>https://youtube.com/watch?v=X_9G5XDbu2M</t>
   </si>
   <si>
     <t>Chef Titouan</t>
   </si>
   <si>
-    <t>_DSC1211.jpeg</t>
-  </si>
-  <si>
     <t>https://youtube.com/watch?v=E0l0B3UQ7mU</t>
   </si>
   <si>
-    <t>_DSC2431-copie.jpeg</t>
-  </si>
-  <si>
     <t>DA BIST is here :O</t>
   </si>
   <si>
@@ -615,12 +654,6 @@
     <t>https://www.youtube.com/shorts/46aVZq8XZ3U</t>
   </si>
   <si>
-    <t>_DSC2427-copie.jpeg</t>
-  </si>
-  <si>
-    <t>_DSC7241-1.jpeg</t>
-  </si>
-  <si>
     <t>https://youtube.com/watch?v=Zk5a15iLbZs</t>
   </si>
   <si>
@@ -630,66 +663,42 @@
     <t>https://youtube.com/watch?v=XuASkDKHsVw</t>
   </si>
   <si>
-    <t>_DSC2801-copie.jpeg</t>
-  </si>
-  <si>
     <t>Soirée entreprise Epsor (longue)</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=T_V5tQPkNsc</t>
   </si>
   <si>
-    <t>_DSC3231-copie.jpeg</t>
-  </si>
-  <si>
     <t>Soirée entreprise Epsor (courte)</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=qCdRKCitbEA</t>
   </si>
   <si>
-    <t>_DSC2635-copie.jpeg</t>
-  </si>
-  <si>
     <t>https://vimeo.com/908241496?share=copy</t>
   </si>
   <si>
-    <t>DSC2922.jpeg</t>
-  </si>
-  <si>
     <t>Évènement Smartbox/Karmine (mobile)</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=DLZMFDOOHMI</t>
   </si>
   <si>
-    <t>_DSC6848-copie.jpeg</t>
-  </si>
-  <si>
     <t>Interview collaborateurs chez Malt</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=tvCDAgxvk_w</t>
   </si>
   <si>
-    <t>DSC5588.jpeg</t>
-  </si>
-  <si>
     <t>Reportage sportif L'Instant Tennis</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=SPPrOZ0zabk</t>
   </si>
   <si>
-    <t>_DSC6800-copie.jpeg</t>
-  </si>
-  <si>
     <t>Interview avec L'Instant Tennis</t>
   </si>
   <si>
-    <t>_DSC3612-copie.jpeg</t>
-  </si>
-  <si>
     <t>https://youtube.com/watch?v=JhiXpdUxxUc</t>
   </si>
   <si>
@@ -699,13 +708,13 @@
     <t>https://vimeo.com/1002458866</t>
   </si>
   <si>
+    <t>_DSC2627-copie.jpeg</t>
+  </si>
+  <si>
     <t>Pub pour une marque dans l'art de la table</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=pFY9UooC-QY</t>
-  </si>
-  <si>
-    <t>_DSC2627-copie.jpeg</t>
   </si>
   <si>
     <t>https://youtube.com/watch?v=ZomLzap8xGE</t>
@@ -775,7 +784,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -794,6 +803,10 @@
       <u/>
       <color rgb="FF000000"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -809,16 +822,19 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1047,23 +1063,22 @@
     <col customWidth="1" min="1" max="1" width="18.13"/>
     <col customWidth="1" min="2" max="2" width="40.5"/>
     <col customWidth="1" min="3" max="3" width="15.75"/>
-    <col customWidth="1" min="4" max="4" width="12.63"/>
     <col customWidth="1" min="5" max="5" width="24.88"/>
     <col customWidth="1" min="6" max="6" width="59.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
@@ -1072,142 +1087,142 @@
         <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>80</v>
+        <v>64</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>99</v>
+        <v>50</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1"/>
@@ -2231,9 +2246,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="59.25"/>
-    <col customWidth="1" min="2" max="2" width="12.63"/>
     <col customWidth="1" min="3" max="3" width="46.88"/>
-    <col customWidth="1" min="4" max="6" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -2241,218 +2254,218 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>10</v>
+      <c r="A2" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>40</v>
+      <c r="A3" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>47</v>
+      <c r="A4" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>51</v>
+      <c r="A5" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>62</v>
+      <c r="A6" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>71</v>
+      <c r="A7" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>78</v>
+      <c r="A8" s="2" t="s">
+        <v>61</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>87</v>
+      <c r="A9" s="2" t="s">
+        <v>65</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>95</v>
+      <c r="A10" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="3" t="s">
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="B17" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>126</v>
+      <c r="A19" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="B21" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>132</v>
+      <c r="A22" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>135</v>
+      <c r="A23" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>141</v>
+      <c r="A25" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>145</v>
+      <c r="A26" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>147</v>
+      <c r="A27" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -3477,37 +3490,35 @@
     <col customWidth="1" min="1" max="1" width="55.25"/>
     <col customWidth="1" min="2" max="2" width="18.25"/>
     <col customWidth="1" min="3" max="3" width="34.13"/>
-    <col customWidth="1" min="4" max="4" width="12.63"/>
     <col customWidth="1" min="5" max="5" width="32.25"/>
-    <col customWidth="1" min="6" max="6" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
+      <c r="A2" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>21</v>
@@ -3517,823 +3528,823 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>23</v>
+      <c r="A3" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>32</v>
+      <c r="A5" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>35</v>
+      <c r="A6" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="A7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>42</v>
+      <c r="A8" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>46</v>
+      <c r="A9" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>50</v>
+      <c r="A10" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>55</v>
+      <c r="A11" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="A12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>70</v>
+      <c r="A13" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>76</v>
+      <c r="A14" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>82</v>
+      <c r="A15" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>90</v>
+      <c r="A16" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>98</v>
+      <c r="A17" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>105</v>
+      <c r="A18" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>109</v>
+      <c r="A19" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>112</v>
+      <c r="A20" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>113</v>
+      <c r="A21" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>117</v>
+      <c r="A22" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>120</v>
+      <c r="A23" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>128</v>
+      <c r="A24" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>131</v>
+      <c r="A25" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>134</v>
+      <c r="A26" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>136</v>
+      <c r="A27" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>140</v>
+      <c r="A28" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>143</v>
+      <c r="A29" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>146</v>
+      <c r="A30" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>148</v>
+      <c r="A31" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3" t="s">
-        <v>151</v>
+      <c r="A32" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>153</v>
+      <c r="A33" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>155</v>
+      <c r="A34" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>158</v>
+      <c r="A35" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3" t="s">
-        <v>160</v>
+      <c r="A36" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>163</v>
+      <c r="A37" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>66</v>
+        <v>173</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>164</v>
+      <c r="A38" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3" t="s">
-        <v>166</v>
+      <c r="A39" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3" t="s">
-        <v>167</v>
+      <c r="A40" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3" t="s">
-        <v>169</v>
+      <c r="A41" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>162</v>
+        <v>99</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3" t="s">
-        <v>170</v>
+      <c r="A42" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>172</v>
+      <c r="A43" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="3" t="s">
-        <v>174</v>
+      <c r="A44" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="3" t="s">
-        <v>177</v>
+      <c r="A45" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3" t="s">
-        <v>178</v>
+      <c r="A46" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3" t="s">
-        <v>181</v>
+      <c r="A47" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="3" t="s">
-        <v>183</v>
+      <c r="A48" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="3" t="s">
-        <v>186</v>
+      <c r="A49" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>187</v>
+        <v>99</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3" t="s">
-        <v>189</v>
+      <c r="A50" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3" t="s">
-        <v>192</v>
+      <c r="A51" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3" t="s">
-        <v>195</v>
+      <c r="A52" s="2" t="s">
+        <v>204</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
-        <v>197</v>
+      <c r="A53" s="2" t="s">
+        <v>206</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3" t="s">
-        <v>200</v>
+      <c r="A54" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="3" t="s">
-        <v>202</v>
+      <c r="A55" s="2" t="s">
+        <v>210</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3" t="s">
-        <v>205</v>
+      <c r="A56" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3" t="s">
-        <v>208</v>
+      <c r="A57" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3" t="s">
-        <v>210</v>
+      <c r="A58" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>104</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="3" t="s">
-        <v>213</v>
+      <c r="A59" s="2" t="s">
+        <v>217</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3" t="s">
-        <v>216</v>
+      <c r="A60" s="2" t="s">
+        <v>218</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3" t="s">
-        <v>219</v>
+      <c r="A61" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>221</v>
@@ -4343,95 +4354,95 @@
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3" t="s">
+      <c r="A62" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C63" s="1" t="s">
+      <c r="D63" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3" t="s">
-        <v>227</v>
-      </c>
       <c r="B64" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3" t="s">
-        <v>229</v>
+      <c r="A65" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>230</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>21</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="2" t="s">
         <v>231</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="3" t="s">
+      <c r="A68" s="2" t="s">
         <v>234</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>235</v>
@@ -4441,39 +4452,39 @@
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="3" t="s">
+      <c r="A69" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3" t="s">
+      <c r="A70" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="3" t="s">
+      <c r="A71" s="2" t="s">
         <v>239</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>240</v>
@@ -4483,81 +4494,81 @@
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="3" t="s">
+      <c r="A72" s="2" t="s">
         <v>241</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>235</v>
+        <v>173</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="3" t="s">
+      <c r="A73" s="2" t="s">
         <v>242</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="3" t="s">
-        <v>243</v>
+      <c r="A74" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="3" t="s">
+      <c r="A75" s="2" t="s">
         <v>245</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="2" t="s">
         <v>248</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>249</v>
@@ -4567,23 +4578,37 @@
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="D78" s="1"/>
-      <c r="E78" s="1" t="str">
-        <f t="shared" ref="E78:E92" si="1">IF(A78:A995="", "", GET_VIDEO_TITLE(A78))</f>
-        <v/>
+      <c r="A78" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="D79" s="1"/>
-      <c r="E79" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="A79" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="D80" s="1"/>
       <c r="E80" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E80:E94" si="1">IF(A80:A997="", "", GET_VIDEO_TITLE(A80))</f>
         <v/>
       </c>
     </row>
@@ -4673,9 +4698,17 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="D93" s="1"/>
+      <c r="E93" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="D94" s="1"/>
+      <c r="E94" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="D95" s="1"/>
@@ -5271,8 +5304,12 @@
     <row r="292" ht="15.75" customHeight="1">
       <c r="D292" s="1"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="D293" s="1"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="D294" s="1"/>
+    </row>
     <row r="295" ht="15.75" customHeight="1"/>
     <row r="296" ht="15.75" customHeight="1"/>
     <row r="297" ht="15.75" customHeight="1"/>
@@ -5979,9 +6016,11 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B77">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B79">
       <formula1>"interview,autre,évènementiel,motion design"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6062,11 +6101,13 @@
     <hyperlink r:id="rId74" ref="A75"/>
     <hyperlink r:id="rId75" ref="A76"/>
     <hyperlink r:id="rId76" ref="A77"/>
+    <hyperlink r:id="rId77" ref="A78"/>
+    <hyperlink r:id="rId78" ref="A79"/>
   </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId77"/>
+  <drawing r:id="rId79"/>
 </worksheet>
 </file>
 
@@ -6080,7 +6121,6 @@
     <col customWidth="1" min="1" max="1" width="79.38"/>
     <col customWidth="1" min="2" max="2" width="26.5"/>
     <col customWidth="1" min="3" max="3" width="40.75"/>
-    <col customWidth="1" min="4" max="6" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -6088,347 +6128,347 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
+      <c r="A2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>77</v>
+      <c r="A9" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>83</v>
+      <c r="A10" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>96</v>
+      <c r="A11" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>102</v>
+      <c r="A12" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>106</v>
+      <c r="A13" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>111</v>
+      <c r="A14" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>115</v>
+      <c r="A15" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>119</v>
+      <c r="A16" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>122</v>
+      <c r="A17" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>137</v>
+      <c r="A18" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>144</v>
+      <c r="A19" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
+      <c r="B25" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>191</v>
+      <c r="A30" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3" t="s">
+      <c r="B38" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="B40" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3" t="s">
-        <v>222</v>
+      <c r="A41" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3" t="s">
-        <v>224</v>
+      <c r="A42" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>228</v>
+      <c r="A43" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1"/>
